--- a/data/trans_orig/P16A_2_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76498</t>
+          <t>74783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112633</t>
+          <t>113420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124277</t>
+          <t>122590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158259</t>
+          <t>156674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209912</t>
+          <t>208026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257927</t>
+          <t>258487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392579</t>
+          <t>391792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428714</t>
+          <t>430429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289208</t>
+          <t>290793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323190</t>
+          <t>324877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694752</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742767</t>
+          <t>744653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75631</t>
+          <t>75538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109937</t>
+          <t>110341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106634</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136761</t>
+          <t>138636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191092</t>
+          <t>192666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238927</t>
+          <t>237681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342276</t>
+          <t>341872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376582</t>
+          <t>376675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>245819</t>
+          <t>243944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275946</t>
+          <t>275653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>595866</t>
+          <t>597112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>643701</t>
+          <t>642127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190014</t>
+          <t>190821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67042</t>
+          <t>67395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88057</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83564</t>
+          <t>90192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281209</t>
+          <t>279501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>478250</t>
+          <t>477443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626770</t>
+          <t>622345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78854</t>
+          <t>78828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99869</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553966</t>
+          <t>555674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>751611</t>
+          <t>744983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>265498</t>
+          <t>263797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325473</t>
+          <t>325947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>368704</t>
+          <t>366251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>728118</t>
+          <t>694402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>643868</t>
+          <t>644084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1136447</t>
+          <t>1192176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709346</t>
+          <t>708872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>769321</t>
+          <t>771022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249976</t>
+          <t>283692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609390</t>
+          <t>611843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>876465</t>
+          <t>820736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1369044</t>
+          <t>1368828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107443</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147592</t>
+          <t>150155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261935</t>
+          <t>275964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>412256</t>
+          <t>414067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409510</t>
+          <t>400928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>539589</t>
+          <t>537376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327454</t>
+          <t>324891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367603</t>
+          <t>365178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429079</t>
+          <t>427268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579400</t>
+          <t>565371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>776792</t>
+          <t>779005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>906871</t>
+          <t>915453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>291760</t>
+          <t>291759</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>268138</t>
+          <t>268873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>315035</t>
+          <t>316705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290979</t>
+          <t>294509</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>353816</t>
+          <t>354941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184063</t>
+          <t>184859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223338</t>
+          <t>222758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>469611</t>
+          <t>469612</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>446336</t>
+          <t>444666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>493233</t>
+          <t>492498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648062</t>
+          <t>646937</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710899</t>
+          <t>707369</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>577363</t>
+          <t>594542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>831716</t>
+          <t>833426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1343811</t>
+          <t>1338469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1908621</t>
+          <t>1894866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2016631</t>
+          <t>2018354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2682823</t>
+          <t>2733136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2544344</t>
+          <t>2542634</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2798697</t>
+          <t>2781518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1669137</t>
+          <t>1682892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2233947</t>
+          <t>2239289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4270995</t>
+          <t>4220682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4937187</t>
+          <t>4935464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_2_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92173</t>
+          <t>105516</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74783</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113420</t>
+          <t>126029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>139976</t>
+          <t>148784</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122590</t>
+          <t>131213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>156674</t>
+          <t>165200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>232149</t>
+          <t>254300</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208026</t>
+          <t>227618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258487</t>
+          <t>278349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>413039</t>
+          <t>445102</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391792</t>
+          <t>424589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430429</t>
+          <t>463174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>307491</t>
+          <t>339627</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290793</t>
+          <t>323211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324877</t>
+          <t>357198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>720530</t>
+          <t>784729</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>760680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744653</t>
+          <t>811411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92503</t>
+          <t>94294</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75538</t>
+          <t>77677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110341</t>
+          <t>112405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106927</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138636</t>
+          <t>151172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>214508</t>
+          <t>227775</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192666</t>
+          <t>204519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237681</t>
+          <t>252996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>359710</t>
+          <t>388918</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341872</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376675</t>
+          <t>405535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>260575</t>
+          <t>289662</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>271971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275653</t>
+          <t>305528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>620285</t>
+          <t>678580</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597112</t>
+          <t>653359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>642127</t>
+          <t>701836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>115017</t>
+          <t>127926</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45919</t>
+          <t>107657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190821</t>
+          <t>148222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>85711</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67395</t>
+          <t>74266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>98023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>192373</t>
+          <t>213637</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90192</t>
+          <t>191753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279501</t>
+          <t>237283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>553247</t>
+          <t>343686</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477443</t>
+          <t>323390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622345</t>
+          <t>363955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89555</t>
+          <t>101786</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78828</t>
+          <t>89474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99516</t>
+          <t>113231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>642802</t>
+          <t>445472</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555674</t>
+          <t>421826</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744983</t>
+          <t>467356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>294198</t>
+          <t>316250</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263797</t>
+          <t>285102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325947</t>
+          <t>347857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>502874</t>
+          <t>332732</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>366251</t>
+          <t>307052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694402</t>
+          <t>356146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>797072</t>
+          <t>648982</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>644084</t>
+          <t>610445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1192176</t>
+          <t>692686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>740621</t>
+          <t>815593</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>708872</t>
+          <t>783986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>771022</t>
+          <t>846741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>475220</t>
+          <t>528479</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283692</t>
+          <t>505065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611843</t>
+          <t>554159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1215840</t>
+          <t>1344072</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>820736</t>
+          <t>1300368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1368828</t>
+          <t>1382609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>128160</t>
+          <t>142753</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109868</t>
+          <t>121563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150155</t>
+          <t>166336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>361792</t>
+          <t>394012</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275964</t>
+          <t>370233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>414067</t>
+          <t>418546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>489952</t>
+          <t>536765</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400928</t>
+          <t>503635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>537376</t>
+          <t>573590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>346886</t>
+          <t>425211</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324891</t>
+          <t>401628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>365178</t>
+          <t>446401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>479543</t>
+          <t>436838</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427268</t>
+          <t>412304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>565371</t>
+          <t>460617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>826429</t>
+          <t>862049</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>779005</t>
+          <t>825224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>915453</t>
+          <t>895179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55648</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>291759</t>
+          <t>314728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>268873</t>
+          <t>291968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316705</t>
+          <t>340804</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>323004</t>
+          <t>341061</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>294509</t>
+          <t>309985</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>354941</t>
+          <t>372299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>209263</t>
+          <t>210895</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184859</t>
+          <t>193098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222758</t>
+          <t>223045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>469612</t>
+          <t>529553</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>444666</t>
+          <t>503477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>492498</t>
+          <t>552313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>678874</t>
+          <t>740448</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>646937</t>
+          <t>709210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>707369</t>
+          <t>771524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>753296</t>
+          <t>813071</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>594542</t>
+          <t>760532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>833426</t>
+          <t>866164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1495762</t>
+          <t>1409448</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1338469</t>
+          <t>1360056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1894866</t>
+          <t>1460974</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2249057</t>
+          <t>2222519</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2018354</t>
+          <t>2146457</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2733136</t>
+          <t>2300088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2622764</t>
+          <t>2629405</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2542634</t>
+          <t>2576312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2781518</t>
+          <t>2681944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2081996</t>
+          <t>2225945</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1682892</t>
+          <t>2174419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2239289</t>
+          <t>2275337</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4704761</t>
+          <t>4855350</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4220682</t>
+          <t>4777781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4935464</t>
+          <t>4931412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
